--- a/Results_experiment/exp_2/preds_1111144422222222.xlsx
+++ b/Results_experiment/exp_2/preds_1111144422222222.xlsx
@@ -924,7 +924,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D2">
-        <v>-5.003419399261475</v>
+        <v>-4.584090232849121</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -938,7 +938,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D3">
-        <v>1.793172001838684</v>
+        <v>2.385703086853027</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -952,7 +952,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D4">
-        <v>0.2302248179912567</v>
+        <v>0.2092000544071198</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -966,7 +966,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D5">
-        <v>1.071271896362305</v>
+        <v>0.5960729718208313</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -980,7 +980,7 @@
         <v>-0.5</v>
       </c>
       <c r="D6">
-        <v>0.9089387655258179</v>
+        <v>1.24946403503418</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -994,7 +994,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D7">
-        <v>-0.8348417282104492</v>
+        <v>0.2865802049636841</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1008,7 +1008,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D8">
-        <v>-0.3590147495269775</v>
+        <v>-0.1358826160430908</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1022,7 +1022,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D9">
-        <v>-3.537801265716553</v>
+        <v>-3.738770008087158</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1036,7 +1036,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D10">
-        <v>-0.04061394929885864</v>
+        <v>-0.03254885971546173</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1050,7 +1050,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D11">
-        <v>-2.540903806686401</v>
+        <v>-2.566838502883911</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1064,7 +1064,7 @@
         <v>-1.5</v>
       </c>
       <c r="D12">
-        <v>3.008739948272705</v>
+        <v>7.662990093231201</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1078,7 +1078,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D13">
-        <v>-0.1185008808970451</v>
+        <v>0.0523402988910675</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1092,7 +1092,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D14">
-        <v>-4.018373966217041</v>
+        <v>-4.043056011199951</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1106,7 +1106,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D15">
-        <v>-2.367337226867676</v>
+        <v>-0.8866702914237976</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1120,7 +1120,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D16">
-        <v>-0.8883292675018311</v>
+        <v>-1.899154424667358</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1134,7 +1134,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D17">
-        <v>-3.628826141357422</v>
+        <v>-3.261350154876709</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1148,7 +1148,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D18">
-        <v>-5.74557638168335</v>
+        <v>-5.162036895751953</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1162,7 +1162,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D19">
-        <v>-0.1010008156299591</v>
+        <v>0.5450329184532166</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1176,7 +1176,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D20">
-        <v>0.1931070983409882</v>
+        <v>0.3789610862731934</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1190,7 +1190,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D21">
-        <v>9.525151252746582</v>
+        <v>10.78860092163086</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1204,7 +1204,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D22">
-        <v>-5.357028484344482</v>
+        <v>-3.602816104888916</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1218,7 +1218,7 @@
         <v>0.5</v>
       </c>
       <c r="D23">
-        <v>-2.881034374237061</v>
+        <v>-3.043131589889526</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1232,7 +1232,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D24">
-        <v>-1.025371551513672</v>
+        <v>2.427707195281982</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1246,7 +1246,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D25">
-        <v>-2.230613708496094</v>
+        <v>-3.296623945236206</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1260,7 +1260,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D26">
-        <v>-3.509831190109253</v>
+        <v>-4.430517673492432</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1274,7 +1274,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D27">
-        <v>-2.342680215835571</v>
+        <v>-2.012916564941406</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1288,7 +1288,7 @@
         <v>4</v>
       </c>
       <c r="D28">
-        <v>1.142769694328308</v>
+        <v>0.9745945334434509</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1302,7 +1302,7 @@
         <v>-5.5</v>
       </c>
       <c r="D29">
-        <v>-4.018101215362549</v>
+        <v>-4.021083354949951</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1316,7 +1316,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D30">
-        <v>-1.980273365974426</v>
+        <v>-1.501807928085327</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1330,7 +1330,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D31">
-        <v>-4.062328815460205</v>
+        <v>-3.833405494689941</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1344,7 +1344,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D32">
-        <v>-0.1874798387289047</v>
+        <v>0.3818202018737793</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1358,7 +1358,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D33">
-        <v>-0.0920078456401825</v>
+        <v>0.2868238091468811</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1372,7 +1372,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D34">
-        <v>0.4512360990047455</v>
+        <v>0.7660205364227295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1386,7 +1386,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D35">
-        <v>-4.035670280456543</v>
+        <v>-3.326691389083862</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1400,7 +1400,7 @@
         <v>-7.5</v>
       </c>
       <c r="D36">
-        <v>-4.78150463104248</v>
+        <v>-3.072917222976685</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1414,7 +1414,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D37">
-        <v>-2.598756313323975</v>
+        <v>-2.481960773468018</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>-3.124813318252563</v>
+        <v>-3.239218711853027</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1442,7 +1442,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D39">
-        <v>0.9320898056030273</v>
+        <v>1.756444215774536</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1456,7 +1456,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D40">
-        <v>0.7401186227798462</v>
+        <v>0.5980857014656067</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1470,7 +1470,7 @@
         <v>11.60000038146973</v>
       </c>
       <c r="D41">
-        <v>2.395637512207031</v>
+        <v>2.241089582443237</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1484,7 +1484,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D42">
-        <v>0.3285632431507111</v>
+        <v>0.2144098877906799</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1498,7 +1498,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D43">
-        <v>-2.751824617385864</v>
+        <v>-2.88843035697937</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1512,7 +1512,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D44">
-        <v>-6.30433988571167</v>
+        <v>-5.230135440826416</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1526,7 +1526,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D45">
-        <v>0.817522406578064</v>
+        <v>0.4765217900276184</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1540,7 +1540,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D46">
-        <v>0.1023695766925812</v>
+        <v>0.6296566128730774</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1554,7 +1554,7 @@
         <v>-6.800000190734863</v>
       </c>
       <c r="D47">
-        <v>-4.823485851287842</v>
+        <v>-3.652585506439209</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1568,7 +1568,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D48">
-        <v>1.381876826286316</v>
+        <v>1.561807155609131</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1582,7 +1582,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D49">
-        <v>-1.742480397224426</v>
+        <v>-0.2255885303020477</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1596,7 +1596,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D50">
-        <v>-4.010324001312256</v>
+        <v>-3.668097496032715</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D51">
-        <v>-1.225314974784851</v>
+        <v>-0.7368974089622498</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>23.29999923706055</v>
       </c>
       <c r="D52">
-        <v>21.44392204284668</v>
+        <v>19.03156280517578</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1638,7 +1638,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D53">
-        <v>0.6666370630264282</v>
+        <v>0.6494570970535278</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D54">
-        <v>3.731054782867432</v>
+        <v>2.551034212112427</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1666,7 +1666,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D55">
-        <v>-0.8404557704925537</v>
+        <v>0.2981850802898407</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D56">
-        <v>1.190293312072754</v>
+        <v>1.319429159164429</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1694,7 +1694,7 @@
         <v>2.5</v>
       </c>
       <c r="D57">
-        <v>1.041192412376404</v>
+        <v>1.3513503074646</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D58">
-        <v>-5.902785778045654</v>
+        <v>-4.604204177856445</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D59">
-        <v>-4.813968181610107</v>
+        <v>-4.10479211807251</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1736,7 +1736,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D60">
-        <v>-0.61219722032547</v>
+        <v>-0.1306925714015961</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D61">
-        <v>1.799167990684509</v>
+        <v>1.93176794052124</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D62">
-        <v>-0.5257546305656433</v>
+        <v>-2.116971731185913</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1778,7 +1778,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D63">
-        <v>-4.047203063964844</v>
+        <v>-4.250278472900391</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1792,7 +1792,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D64">
-        <v>1.828638434410095</v>
+        <v>2.033319234848022</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1806,7 +1806,7 @@
         <v>-1</v>
       </c>
       <c r="D65">
-        <v>1.594185948371887</v>
+        <v>2.458543300628662</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1820,7 +1820,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D66">
-        <v>1.897440791130066</v>
+        <v>1.811741590499878</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D67">
-        <v>-4.144961833953857</v>
+        <v>-2.952712297439575</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D68">
-        <v>-0.1634411811828613</v>
+        <v>-0.2447364330291748</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>-11.19999980926514</v>
       </c>
       <c r="D69">
-        <v>-8.445418357849121</v>
+        <v>-8.148820877075195</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>0.05473637580871582</v>
+        <v>-0.1944407522678375</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D71">
-        <v>-2.657939434051514</v>
+        <v>-2.517299890518188</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1904,7 +1904,7 @@
         <v>-2</v>
       </c>
       <c r="D72">
-        <v>1.651421427726746</v>
+        <v>0.3086307644844055</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1918,7 +1918,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D73">
-        <v>0.2177901268005371</v>
+        <v>0.6018478870391846</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D74">
-        <v>-0.1801911294460297</v>
+        <v>-0.218875989317894</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D75">
-        <v>-0.3016072511672974</v>
+        <v>-1.061973810195923</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1960,7 +1960,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D76">
-        <v>-3.44990873336792</v>
+        <v>-3.136367321014404</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1974,7 +1974,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D77">
-        <v>-0.2452802211046219</v>
+        <v>-0.2242715954780579</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D78">
-        <v>-0.7862752676010132</v>
+        <v>0.9258071780204773</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D79">
-        <v>1.356999516487122</v>
+        <v>2.349637746810913</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D80">
-        <v>-1.524184346199036</v>
+        <v>-1.571040630340576</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D81">
-        <v>-0.4637357592582703</v>
+        <v>0.114832729101181</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D82">
-        <v>0.1171517968177795</v>
+        <v>-0.0298902690410614</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D83">
-        <v>0.2863555252552032</v>
+        <v>0.3063149154186249</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>-6</v>
       </c>
       <c r="D84">
-        <v>-7.150533199310303</v>
+        <v>-6.945881366729736</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>0.5</v>
       </c>
       <c r="D85">
-        <v>1.147725105285645</v>
+        <v>1.732944250106812</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D86">
-        <v>1.314893126487732</v>
+        <v>1.73572301864624</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D87">
-        <v>-3.190313816070557</v>
+        <v>-3.728789806365967</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D88">
-        <v>1.153293132781982</v>
+        <v>1.020350694656372</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D89">
-        <v>-0.8520039319992065</v>
+        <v>-0.05558551847934723</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D90">
-        <v>-4.834646701812744</v>
+        <v>-3.505492687225342</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D91">
-        <v>-6.146543025970459</v>
+        <v>-6.858685970306396</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D92">
-        <v>-0.1317113488912582</v>
+        <v>-4.870523452758789</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D93">
-        <v>-3.17332124710083</v>
+        <v>-5.152429580688477</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D94">
-        <v>-2.232771873474121</v>
+        <v>-3.042750597000122</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D95">
-        <v>-0.1708689779043198</v>
+        <v>-0.3039088845252991</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D96">
-        <v>-0.007683038711547852</v>
+        <v>0.1746586561203003</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D97">
-        <v>-4.540619373321533</v>
+        <v>-3.950733661651611</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D98">
-        <v>-7.992489337921143</v>
+        <v>-7.015453338623047</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D99">
-        <v>-9.579432487487793</v>
+        <v>-8.588639259338379</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D100">
-        <v>0.09827873110771179</v>
+        <v>-0.5338347554206848</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D101">
-        <v>-4.613824844360352</v>
+        <v>-2.918049573898315</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D102">
-        <v>-0.01351320743560791</v>
+        <v>0.1177049279212952</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D103">
-        <v>0.1991575062274933</v>
+        <v>0.5432096719741821</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D104">
-        <v>4.674134254455566</v>
+        <v>6.042276859283447</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D105">
-        <v>1.063174962997437</v>
+        <v>1.751382112503052</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D106">
-        <v>-0.4029850959777832</v>
+        <v>-0.06341354548931122</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>-11.39999961853027</v>
       </c>
       <c r="D107">
-        <v>-8.90323543548584</v>
+        <v>-7.766812801361084</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D108">
-        <v>1.568344116210938</v>
+        <v>1.203993558883667</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D109">
-        <v>-3.401488542556763</v>
+        <v>-4.472368240356445</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D110">
-        <v>-3.32773494720459</v>
+        <v>-3.110749244689941</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D111">
-        <v>-3.14959192276001</v>
+        <v>-2.640428781509399</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D112">
-        <v>0.9187635183334351</v>
+        <v>0.2436435222625732</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D113">
-        <v>-2.604957103729248</v>
+        <v>-2.496184110641479</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D114">
-        <v>-5.825817584991455</v>
+        <v>-4.942189693450928</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D115">
-        <v>1.043388366699219</v>
+        <v>0.7663928866386414</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>-2</v>
       </c>
       <c r="D116">
-        <v>0.2511695921421051</v>
+        <v>0.3124477863311768</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D117">
-        <v>-0.1824039220809937</v>
+        <v>0.3181833624839783</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D118">
-        <v>0.3425100743770599</v>
+        <v>1.155524253845215</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>-5.5</v>
       </c>
       <c r="D119">
-        <v>-4.541292667388916</v>
+        <v>-4.465997695922852</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D120">
-        <v>0.4433101117610931</v>
+        <v>1.101227760314941</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D121">
-        <v>1.046738982200623</v>
+        <v>1.103791475296021</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D122">
-        <v>2.849058628082275</v>
+        <v>2.468858480453491</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D123">
-        <v>-6.127613544464111</v>
+        <v>-3.088592767715454</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>-6</v>
       </c>
       <c r="D124">
-        <v>-2.790836572647095</v>
+        <v>-2.811909437179565</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D125">
-        <v>0.9920668601989746</v>
+        <v>1.164136648178101</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>-3.5</v>
       </c>
       <c r="D126">
-        <v>-2.698684453964233</v>
+        <v>-2.353321313858032</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D127">
-        <v>-11.53401947021484</v>
+        <v>-9.456731796264648</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D128">
-        <v>0.5539617538452148</v>
+        <v>0.4898809790611267</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D129">
-        <v>-3.888788223266602</v>
+        <v>-3.234480857849121</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D130">
-        <v>0.6057428121566772</v>
+        <v>0.3468394875526428</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D131">
-        <v>1.980032801628113</v>
+        <v>2.38404655456543</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="D132">
-        <v>1.485017895698547</v>
+        <v>0.7243810892105103</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D133">
-        <v>-4.017903327941895</v>
+        <v>-5.121682643890381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D134">
-        <v>2.113700389862061</v>
+        <v>1.534242153167725</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>2.5</v>
       </c>
       <c r="D135">
-        <v>0.3980573713779449</v>
+        <v>0.9075952172279358</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D136">
-        <v>5.876772403717041</v>
+        <v>5.95071268081665</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D137">
-        <v>1.494518160820007</v>
+        <v>1.320142269134521</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D138">
-        <v>-0.4502666890621185</v>
+        <v>-0.07371852546930313</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D139">
-        <v>-0.9142304658889771</v>
+        <v>0.2208603620529175</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D140">
-        <v>2.666877269744873</v>
+        <v>3.838858366012573</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>-14.5</v>
       </c>
       <c r="D141">
-        <v>-4.665029525756836</v>
+        <v>-2.992288827896118</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D142">
-        <v>-2.267953634262085</v>
+        <v>-1.784385204315186</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D143">
-        <v>-0.2243174612522125</v>
+        <v>-0.05901119112968445</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D144">
-        <v>0.386164516210556</v>
+        <v>-0.923561155796051</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D145">
-        <v>-0.8917149305343628</v>
+        <v>-0.911865770816803</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>-12</v>
       </c>
       <c r="D146">
-        <v>-10.01796627044678</v>
+        <v>-10.37517738342285</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>-12.5</v>
       </c>
       <c r="D147">
-        <v>-9.00649356842041</v>
+        <v>-8.471529006958008</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2968,7 +2968,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D148">
-        <v>-0.1693121492862701</v>
+        <v>-0.07027192413806915</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>-0.1153228357434273</v>
+        <v>-0.06794662773609161</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2996,7 +2996,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D150">
-        <v>0.007352754473686218</v>
+        <v>0.2093974351882935</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3010,7 +3010,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D151">
-        <v>0.7804882526397705</v>
+        <v>0.7193598747253418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>1.5</v>
       </c>
       <c r="D152">
-        <v>1.01288640499115</v>
+        <v>0.9922987818717957</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3038,7 +3038,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D153">
-        <v>0.9024721384048462</v>
+        <v>1.211208820343018</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3052,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="D154">
-        <v>1.905309796333313</v>
+        <v>2.263396978378296</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>-6.800000190734863</v>
       </c>
       <c r="D155">
-        <v>-4.842025756835938</v>
+        <v>-5.144618988037109</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D156">
-        <v>1.273397564888</v>
+        <v>2.087754964828491</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D157">
-        <v>0.05833277106285095</v>
+        <v>0.140471875667572</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3108,7 +3108,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D158">
-        <v>3.028758764266968</v>
+        <v>3.128810167312622</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3122,7 +3122,7 @@
         <v>-9.5</v>
       </c>
       <c r="D159">
-        <v>-6.055192947387695</v>
+        <v>-5.639037609100342</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3136,7 +3136,7 @@
         <v>-5.5</v>
       </c>
       <c r="D160">
-        <v>-3.725958585739136</v>
+        <v>-4.445940494537354</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D161">
-        <v>1.719407916069031</v>
+        <v>1.79802393913269</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3164,7 +3164,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D162">
-        <v>1.806511998176575</v>
+        <v>1.533575296401978</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3178,7 +3178,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D163">
-        <v>1.098546028137207</v>
+        <v>1.137306451797485</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3192,7 +3192,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D164">
-        <v>0.2881557643413544</v>
+        <v>0.8681432604789734</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3206,7 +3206,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D165">
-        <v>1.422532916069031</v>
+        <v>1.567532539367676</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3220,7 +3220,7 @@
         <v>-3</v>
       </c>
       <c r="D166">
-        <v>-1.410995483398438</v>
+        <v>-1.222723960876465</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D167">
-        <v>-5.780405044555664</v>
+        <v>-4.697817325592041</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D168">
-        <v>0.566888689994812</v>
+        <v>0.563234269618988</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3262,7 +3262,7 @@
         <v>2</v>
       </c>
       <c r="D169">
-        <v>1.316029191017151</v>
+        <v>0.8694203495979309</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3276,7 +3276,7 @@
         <v>-5</v>
       </c>
       <c r="D170">
-        <v>0.2529473304748535</v>
+        <v>-0.1896480023860931</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D171">
-        <v>-2.674461126327515</v>
+        <v>-2.082497119903564</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3304,7 +3304,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D172">
-        <v>-4.110314846038818</v>
+        <v>-3.408648252487183</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3318,7 +3318,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D173">
-        <v>-2.356015205383301</v>
+        <v>-1.002479553222656</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D174">
-        <v>2.680997133255005</v>
+        <v>4.189978122711182</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3346,7 +3346,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D175">
-        <v>0.1453295946121216</v>
+        <v>0.5392881035804749</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>1.5</v>
       </c>
       <c r="D176">
-        <v>-0.1390005052089691</v>
+        <v>0.3024906516075134</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3374,7 +3374,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D177">
-        <v>-0.4580098688602448</v>
+        <v>0.1501103043556213</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3388,7 +3388,7 @@
         <v>-3.5</v>
       </c>
       <c r="D178">
-        <v>0.4510379731655121</v>
+        <v>0.5581456422805786</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D179">
-        <v>-1.074247598648071</v>
+        <v>-0.1412607133388519</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3416,7 +3416,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D180">
-        <v>0.9620093107223511</v>
+        <v>0.8534229397773743</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3430,7 +3430,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D181">
-        <v>1.25666880607605</v>
+        <v>2.136361837387085</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3444,7 +3444,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D182">
-        <v>-5.650804042816162</v>
+        <v>-5.181329250335693</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3458,7 +3458,7 @@
         <v>-1.5</v>
       </c>
       <c r="D183">
-        <v>-3.175179958343506</v>
+        <v>-4.381774425506592</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3472,7 +3472,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D184">
-        <v>-8.287518501281738</v>
+        <v>-7.680984973907471</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3486,7 +3486,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D185">
-        <v>-2.843768835067749</v>
+        <v>-2.571899175643921</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3500,7 +3500,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D186">
-        <v>0.7500972747802734</v>
+        <v>-0.2629714608192444</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3514,7 +3514,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D187">
-        <v>-1.496061444282532</v>
+        <v>-1.976439476013184</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3528,7 +3528,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D188">
-        <v>-0.891121506690979</v>
+        <v>0.2665176093578339</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3542,7 +3542,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D189">
-        <v>-2.857356071472168</v>
+        <v>-2.108056306838989</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D190">
-        <v>0.1804420948028564</v>
+        <v>-1.049551725387573</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3570,7 +3570,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D191">
-        <v>-0.153101921081543</v>
+        <v>0.3281548619270325</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3584,7 +3584,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D192">
-        <v>-6.641650676727295</v>
+        <v>-6.01190710067749</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3598,7 +3598,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D193">
-        <v>-3.416139125823975</v>
+        <v>-3.479045391082764</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3612,7 +3612,7 @@
         <v>-2.5</v>
       </c>
       <c r="D194">
-        <v>0.4189423620700836</v>
+        <v>0.7621528506278992</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3626,7 +3626,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D195">
-        <v>-2.423075199127197</v>
+        <v>-0.3896059989929199</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3640,7 +3640,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D196">
-        <v>-0.03893905878067017</v>
+        <v>0.8435763716697693</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3654,7 +3654,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D197">
-        <v>-0.1114452928304672</v>
+        <v>0.4417456984519958</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3668,7 +3668,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D198">
-        <v>1.468464255332947</v>
+        <v>1.552862644195557</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3682,7 +3682,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D199">
-        <v>-4.675713062286377</v>
+        <v>-3.035299301147461</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3696,7 +3696,7 @@
         <v>2.5</v>
       </c>
       <c r="D200">
-        <v>1.171656966209412</v>
+        <v>1.180482387542725</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>2.5</v>
       </c>
       <c r="D201">
-        <v>-3.993629932403564</v>
+        <v>-4.477619647979736</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3724,7 +3724,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D202">
-        <v>3.546065330505371</v>
+        <v>5.134974956512451</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D203">
-        <v>1.356708407402039</v>
+        <v>0.7504642605781555</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3752,7 +3752,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D204">
-        <v>-1.609267354011536</v>
+        <v>-0.9375600218772888</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3766,7 +3766,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D205">
-        <v>0.2167264819145203</v>
+        <v>0.1435405015945435</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3780,7 +3780,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D206">
-        <v>-5.210835933685303</v>
+        <v>-4.397868633270264</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3794,7 +3794,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D207">
-        <v>-1.987331032752991</v>
+        <v>-1.96738338470459</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3808,7 +3808,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D208">
-        <v>1.077472805976868</v>
+        <v>1.28784966468811</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D209">
-        <v>-9.659163475036621</v>
+        <v>-8.364986419677734</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D210">
-        <v>-2.873976707458496</v>
+        <v>-3.205927133560181</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3850,7 +3850,7 @@
         <v>-1.5</v>
       </c>
       <c r="D211">
-        <v>-5.446938514709473</v>
+        <v>-5.166627407073975</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D212">
-        <v>-0.1791586726903915</v>
+        <v>-0.09091682732105255</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3878,7 +3878,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D213">
-        <v>-5.227211475372314</v>
+        <v>-4.420225620269775</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3892,7 +3892,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D214">
-        <v>0.6018478870391846</v>
+        <v>0.6401518583297729</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3906,7 +3906,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D215">
-        <v>-3.093233346939087</v>
+        <v>-2.711982011795044</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3920,7 +3920,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D216">
-        <v>-1.054705739021301</v>
+        <v>-0.4387029111385345</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3934,7 +3934,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D217">
-        <v>-1.654902815818787</v>
+        <v>0.3067771792411804</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3948,7 +3948,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D218">
-        <v>0.1227706670761108</v>
+        <v>0.2004425525665283</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>-2.5</v>
       </c>
       <c r="D219">
-        <v>-1.955689549446106</v>
+        <v>0.01289515197277069</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3976,7 +3976,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D220">
-        <v>-3.423591613769531</v>
+        <v>-2.841842889785767</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3990,7 +3990,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D221">
-        <v>-1.240893244743347</v>
+        <v>-0.2355629205703735</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4004,7 +4004,7 @@
         <v>-3.5</v>
       </c>
       <c r="D222">
-        <v>0.724817156791687</v>
+        <v>-1.42457389831543</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4018,7 +4018,7 @@
         <v>-6</v>
       </c>
       <c r="D223">
-        <v>-2.12959885597229</v>
+        <v>-4.750363826751709</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4032,7 +4032,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D224">
-        <v>-8.850836753845215</v>
+        <v>-7.841514587402344</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4046,7 +4046,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D225">
-        <v>-4.683213710784912</v>
+        <v>-3.476349830627441</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4060,7 +4060,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D226">
-        <v>1.02158522605896</v>
+        <v>1.439031362533569</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4074,7 +4074,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D227">
-        <v>-3.04381275177002</v>
+        <v>-3.064589500427246</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4088,7 +4088,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D228">
-        <v>-5.287824153900146</v>
+        <v>-4.868043422698975</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4102,7 +4102,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D229">
-        <v>6.90956974029541</v>
+        <v>6.153377532958984</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4116,7 +4116,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D230">
-        <v>-6.339811325073242</v>
+        <v>-6.570366859436035</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4130,7 +4130,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D231">
-        <v>-4.948750019073486</v>
+        <v>-4.132240295410156</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4144,7 +4144,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D232">
-        <v>-1.749701380729675</v>
+        <v>-0.5808571577072144</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4158,7 +4158,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D233">
-        <v>0.632843017578125</v>
+        <v>-0.2049323618412018</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="D234">
-        <v>-7.094786167144775</v>
+        <v>-3.839680910110474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4186,7 +4186,7 @@
         <v>-4</v>
       </c>
       <c r="D235">
-        <v>0.1578703224658966</v>
+        <v>0.5703797936439514</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4200,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="D236">
-        <v>1.775439858436584</v>
+        <v>2.066367149353027</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4214,7 +4214,7 @@
         <v>8</v>
       </c>
       <c r="D237">
-        <v>2.344189882278442</v>
+        <v>2.812196493148804</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4228,7 +4228,7 @@
         <v>-10</v>
       </c>
       <c r="D238">
-        <v>-9.863469123840332</v>
+        <v>-9.044755935668945</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4242,7 +4242,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D239">
-        <v>-8.663178443908691</v>
+        <v>-8.783205032348633</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4256,7 +4256,7 @@
         <v>19</v>
       </c>
       <c r="D240">
-        <v>13.62588596343994</v>
+        <v>12.66290473937988</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4270,7 +4270,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D241">
-        <v>-1.416188359260559</v>
+        <v>-0.7879588007926941</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4284,7 +4284,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D242">
-        <v>0.6755139827728271</v>
+        <v>1.315284252166748</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4298,7 +4298,7 @@
         <v>-3</v>
       </c>
       <c r="D243">
-        <v>-1.455800414085388</v>
+        <v>-0.3775348365306854</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4312,7 +4312,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D244">
-        <v>-3.618685722351074</v>
+        <v>-3.331487894058228</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4326,7 +4326,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D245">
-        <v>5.127025127410889</v>
+        <v>5.209859371185303</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4340,7 +4340,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D246">
-        <v>1.052372574806213</v>
+        <v>1.407819986343384</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4354,7 +4354,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D247">
-        <v>-7.818849086761475</v>
+        <v>-7.416133403778076</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4368,7 +4368,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D248">
-        <v>0.4207489192485809</v>
+        <v>0.5340680480003357</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>8</v>
       </c>
       <c r="D249">
-        <v>1.464114546775818</v>
+        <v>2.303064584732056</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4396,7 +4396,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D250">
-        <v>-9.854617118835449</v>
+        <v>-9.028505325317383</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4410,7 +4410,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D251">
-        <v>-3.723493814468384</v>
+        <v>-4.136512756347656</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4424,7 +4424,7 @@
         <v>-7</v>
       </c>
       <c r="D252">
-        <v>-5.375881671905518</v>
+        <v>-5.236981868743896</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4438,7 +4438,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D253">
-        <v>-6.775851249694824</v>
+        <v>-6.812949657440186</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4452,7 +4452,7 @@
         <v>0.5</v>
       </c>
       <c r="D254">
-        <v>0.6370936632156372</v>
+        <v>0.4117756485939026</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4466,7 +4466,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D255">
-        <v>1.003178954124451</v>
+        <v>0.632862389087677</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4480,7 +4480,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D256">
-        <v>-4.697707653045654</v>
+        <v>-2.809059619903564</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4494,7 +4494,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D257">
-        <v>0.7427341938018799</v>
+        <v>1.063183069229126</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D258">
-        <v>-2.597293376922607</v>
+        <v>-2.635595083236694</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4522,7 +4522,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D259">
-        <v>-0.05356279015541077</v>
+        <v>-0.4135900437831879</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4536,7 +4536,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D260">
-        <v>0.01554769277572632</v>
+        <v>-0.3230885863304138</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4550,7 +4550,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D261">
-        <v>-0.128058597445488</v>
+        <v>-0.06484471261501312</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4564,7 +4564,7 @@
         <v>-7.699999809265137</v>
       </c>
       <c r="D262">
-        <v>-1.707522749900818</v>
+        <v>-2.735566854476929</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D263">
-        <v>-3.262690544128418</v>
+        <v>-0.1805003583431244</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D264">
-        <v>-1.019494652748108</v>
+        <v>-1.061551213264465</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4606,7 +4606,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D265">
-        <v>1.231688380241394</v>
+        <v>1.543140172958374</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4620,7 +4620,7 @@
         <v>-10.19999980926514</v>
       </c>
       <c r="D266">
-        <v>-7.651586532592773</v>
+        <v>-6.758827209472656</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4634,7 +4634,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D267">
-        <v>1.484367251396179</v>
+        <v>2.541600465774536</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4648,7 +4648,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D268">
-        <v>1.265138387680054</v>
+        <v>1.531194925308228</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4662,7 +4662,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D269">
-        <v>-1.513558268547058</v>
+        <v>-1.639926433563232</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4676,7 +4676,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D270">
-        <v>-2.685100078582764</v>
+        <v>-2.725858688354492</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4690,7 +4690,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D271">
-        <v>0.7367153167724609</v>
+        <v>0.4679508805274963</v>
       </c>
     </row>
   </sheetData>
